--- a/data-manipulation-scripts/sheets-cleanup/sheets/SUPORTE PARALAMA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SUPORTE PARALAMA - 29_01.xlsx
@@ -28,13 +28,13 @@
     <t>7896963613981</t>
   </si>
   <si>
-    <t>SUPORTE PARALAMA CETRAL POLIMET CB300E 2009 A 2015 101500427</t>
+    <t>SUPORTE PARALAMA CENTRAL POLIMET CB300E 2009 A 2015 101500427</t>
   </si>
   <si>
     <t>5900029146497</t>
   </si>
   <si>
-    <t>SUPORTE PARALAMA CETRAL EMBUS CG TITAN150 2004 A 2013/ FAN125-150 2009 A 2017 14311</t>
+    <t>SUPORTE PARALAMA CENTRAL EMBUS CG TITAN150 2004 A 2013/ FAN125-150 2009 A 2017 14311</t>
   </si>
   <si>
     <t>SUPORTE PARALAMA SMARTFOX TITAN CG125 KS/ FAN125</t>
@@ -61,7 +61,7 @@
     <t>618341659643</t>
   </si>
   <si>
-    <t>SUPORTE PARALAMA CETRAL IRON TITAN FAN160 136826</t>
+    <t>SUPORTE PARALAMA CENTRAL IRON TITAN FAN160 136826</t>
   </si>
 </sst>
 </file>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/SUPORTE PARALAMA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SUPORTE PARALAMA - 29_01.xlsx
@@ -405,7 +405,9 @@
       <c r="C5" s="2">
         <v>4.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -457,7 +459,9 @@
       <c r="C9" s="2">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
